--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BN3PEPF00001EB3\EXCELCNV\e898315e-d6fe-4d6a-9b2a-36efd5300fce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD63BAB-92C2-443B-BF25-08BC5EFAEC32}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Usuario" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>SIMULADOR DE PRÉSTAMOS – EL SALVADOR</t>
   </si>
@@ -88,29 +88,86 @@
     <t>Banco Azul</t>
   </si>
   <si>
-    <t>Cuota Base</t>
-  </si>
-  <si>
-    <t>Seguro Mensual</t>
-  </si>
-  <si>
-    <t>Cuota Total</t>
-  </si>
-  <si>
-    <t>Comisión</t>
-  </si>
-  <si>
-    <t>Costo Total</t>
-  </si>
-  <si>
     <t>Evaluación</t>
+  </si>
+  <si>
+    <t>Banco Promerica</t>
+  </si>
+  <si>
+    <t>Banco G&amp;T Continental</t>
+  </si>
+  <si>
+    <t>Banco Abank</t>
+  </si>
+  <si>
+    <t>Banco Atlántida SV</t>
+  </si>
+  <si>
+    <t>Banco Integral</t>
+  </si>
+  <si>
+    <t>Banco Multivalores</t>
+  </si>
+  <si>
+    <t>Financiera Credicomer</t>
+  </si>
+  <si>
+    <t>Financiera Fiducia</t>
+  </si>
+  <si>
+    <t>FEDECACES</t>
+  </si>
+  <si>
+    <t>CACEP</t>
+  </si>
+  <si>
+    <t>ACODJAR</t>
+  </si>
+  <si>
+    <t>COOPAS</t>
+  </si>
+  <si>
+    <t>CREDESAN</t>
+  </si>
+  <si>
+    <t>Caja de Crédito Zacatecoluca</t>
+  </si>
+  <si>
+    <t>Caja de Crédito San Miguel</t>
+  </si>
+  <si>
+    <t>Caja de Crédito Metapán</t>
+  </si>
+  <si>
+    <t>AMC</t>
+  </si>
+  <si>
+    <t>FUNDAMICRO</t>
+  </si>
+  <si>
+    <t>Cuota Base $</t>
+  </si>
+  <si>
+    <t>Seguro Mensual $</t>
+  </si>
+  <si>
+    <t>Cuota Total $</t>
+  </si>
+  <si>
+    <t>Comisión $</t>
+  </si>
+  <si>
+    <t>Costo Total $</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,14 +179,30 @@
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,8 +224,32 @@
         <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor rgb="FFB8CCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -160,24 +257,234 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F1"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F1"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F1"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F1"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F1"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -188,6 +495,43 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{080ABFE9-80C2-4A58-8BC4-BBCA16057D04}" name="Tabla1" displayName="Tabla1" ref="A1:D25" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9">
+  <autoFilter ref="A1:D25" xr:uid="{080ABFE9-80C2-4A58-8BC4-BBCA16057D04}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{AA2A3659-7672-4F99-885E-610FAC14686C}" name="Banco" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{C4781AEF-B664-4AF5-895A-39D0F39F0B17}" name="Tasa Anual (%)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{8E36FA80-3834-4E12-8186-2824F196B054}" name="Comisión Apertura (%)" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{4F8D4ED9-5269-4616-9C6D-A121FCF25265}" name="Seguro Mensual (%)" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264891E1-080E-4BAC-9BA3-AA23FF7A4EFB}" name="Tabla3" displayName="Tabla3" ref="A1:G25" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:G25" xr:uid="{264891E1-080E-4BAC-9BA3-AA23FF7A4EFB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F5BA89DD-0F6B-44A0-995C-9B338E879CC5}" name="Banco">
+      <calculatedColumnFormula>Bancos!A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{86DBCBAC-4201-4193-A97D-A1E2B1CCDF8D}" name="Cuota Base $" dataDxfId="0">
+      <calculatedColumnFormula>-PMT(Bancos!B2/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{2859AA11-281A-460E-B9E9-B120708B86A6}" name="Seguro Mensual $">
+      <calculatedColumnFormula>Datos_Usuario!$B$2*Bancos!D2/100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{35FF3CC9-8643-471C-8783-0366014B943E}" name="Cuota Total $" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{64796EF2-7559-4746-9DE2-7E951923F98F}" name="Comisión $" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{D6134B07-6059-4D61-B517-A15DC0DE93AB}" name="Costo Total $" dataDxfId="3">
+      <calculatedColumnFormula>($D$2*Datos_Usuario!$B$3)+E2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{294D65C5-04E3-49E2-88F6-6F3C4957DEC8}" name="Evaluación"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,59 +819,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="13">
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="14">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="13">
         <v>800</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="14">
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <f>B3*B4</f>
-        <v>28800</v>
-      </c>
+      <c r="B6" s="13">
+        <f>B5*B4</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -539,303 +887,1029 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>15.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>2</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="8">
         <v>17</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>1.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>16</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>0.45</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <v>16.5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>1.2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>14.5</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>0.35</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
+        <v>12.2</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7">
-        <v>1.3</v>
-      </c>
-      <c r="D7">
+      <c r="B9" s="8">
+        <v>18.5</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>19</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="8">
+        <v>18.2</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="D11" s="8">
         <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="8">
+        <v>19.8</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7">
+        <v>21</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="8">
+        <v>22.5</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="8">
+        <v>15.9</v>
+      </c>
+      <c r="C19" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="8">
+        <v>22</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="8">
+        <v>21.8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="7">
+        <v>24</v>
+      </c>
+      <c r="C24" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="8">
+        <v>26.5</v>
+      </c>
+      <c r="C25" s="8">
+        <v>4</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>Bancos!A2</f>
         <v>Banco Agrícola</v>
       </c>
-      <c r="B2">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B2/100/12,Datos_Usuario!B3,Datos_Usuario!B2))</f>
+      <c r="B2" s="9">
+        <f>-PMT(Bancos!B2/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>349.10681021795432</v>
       </c>
       <c r="C2">
-        <f>Datos_Usuario!B2*Bancos!D2/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D2/100</f>
         <v>40</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D7" si="0">B2+C2</f>
+      <c r="D2" s="9">
+        <f t="shared" ref="D2:D25" si="0">B2+C2</f>
         <v>389.10681021795432</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <f>Datos_Usuario!B2*Bancos!C2/100</f>
         <v>200</v>
       </c>
-      <c r="F2">
-        <f>(D2*Datos_Usuario!B3)+E2</f>
+      <c r="F2" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E2</f>
         <v>14207.845167846355</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>Bancos!A3</f>
         <v>BAC Credomatic</v>
       </c>
-      <c r="B3">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B3/100/12,Datos_Usuario!B4,Datos_Usuario!B3))</f>
-        <v>0.5100066086090036</v>
+      <c r="B3" s="9">
+        <f>-PMT(Bancos!B3/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>356.52727526744678</v>
       </c>
       <c r="C3">
-        <f>Datos_Usuario!B2*Bancos!D3/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D3/100</f>
         <v>50</v>
       </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>50.510006608609004</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="9">
+        <f t="shared" si="0"/>
+        <v>406.52727526744678</v>
+      </c>
+      <c r="E3" s="9">
         <f>Datos_Usuario!B2*Bancos!C3/100</f>
         <v>150</v>
       </c>
-      <c r="F3">
-        <f>(D3*Datos_Usuario!B3)+E3</f>
-        <v>1968.3602379099241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E3</f>
+        <v>14157.845167846355</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>Bancos!A4</f>
         <v>Banco Cuscatlán</v>
       </c>
-      <c r="B4">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B4/100/12,Datos_Usuario!B5,Datos_Usuario!B4))</f>
-        <v>2689.7420648357679</v>
+      <c r="B4" s="9">
+        <f>-PMT(Bancos!B4/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>351.57033036350094</v>
       </c>
       <c r="C4">
-        <f>Datos_Usuario!B2*Bancos!D4/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D4/100</f>
         <v>45</v>
       </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>2734.7420648357679</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="9">
+        <f t="shared" si="0"/>
+        <v>396.57033036350094</v>
+      </c>
+      <c r="E4" s="9">
         <f>Datos_Usuario!B2*Bancos!C4/100</f>
         <v>100</v>
       </c>
-      <c r="F4">
-        <f>(D4*Datos_Usuario!B3)+E4</f>
-        <v>98550.71433408765</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E4</f>
+        <v>14107.845167846355</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>Bancos!A5</f>
         <v>Davivienda</v>
       </c>
-      <c r="B5">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B5/100/12,Datos_Usuario!B6,Datos_Usuario!B5))</f>
-        <v>4.1250000000000002E-3</v>
+      <c r="B5" s="9">
+        <f>-PMT(Bancos!B5/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>354.04382550022973</v>
       </c>
       <c r="C5">
-        <f>Datos_Usuario!B2*Bancos!D5/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D5/100</f>
         <v>50</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>50.004125000000002</v>
-      </c>
-      <c r="E5">
-        <f>Datos_Usuario!B2*Bancos!C5/100</f>
+      <c r="D5" s="9">
+        <f>B5+C5</f>
+        <v>404.04382550022973</v>
+      </c>
+      <c r="E5" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C5/100</f>
         <v>120</v>
       </c>
-      <c r="F5">
-        <f>(D5*Datos_Usuario!B3)+E5</f>
-        <v>1920.1485</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E5</f>
+        <v>14127.845167846355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>Bancos!A6</f>
         <v>Banco Hipotecario</v>
       </c>
-      <c r="B6" t="e">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B6/100/12,Datos_Usuario!B7,Datos_Usuario!B6))</f>
-        <v>#NUM!</v>
+      <c r="B6" s="9">
+        <f>-PMT(Bancos!B6/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>344.20977442813734</v>
       </c>
       <c r="C6">
-        <f>Datos_Usuario!B2*Bancos!D6/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D6/100</f>
         <v>35</v>
       </c>
-      <c r="D6" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="E6">
-        <f>Datos_Usuario!B2*Bancos!C6/100</f>
+      <c r="D6" s="9">
+        <f>B6+C6</f>
+        <v>379.20977442813734</v>
+      </c>
+      <c r="E6" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C6/100</f>
         <v>100</v>
       </c>
-      <c r="F6" t="e">
-        <f>(D6*Datos_Usuario!B3)+E6</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E6</f>
+        <v>14107.845167846355</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>Bancos!A7</f>
         <v>Banco Azul</v>
       </c>
-      <c r="B7" t="e">
-        <f>-_xlfn.SINGLE(PMT(Bancos!B7/100/12,Datos_Usuario!B8,Datos_Usuario!B7))</f>
-        <v>#NUM!</v>
+      <c r="B7" s="9">
+        <f>-PMT(Bancos!B7/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>333.09914727809905</v>
       </c>
       <c r="C7">
-        <f>Datos_Usuario!B2*Bancos!D7/100</f>
+        <f>Datos_Usuario!$B$2*Bancos!D7/100</f>
         <v>55</v>
       </c>
-      <c r="D7" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="E7">
-        <f>Datos_Usuario!B2*Bancos!C7/100</f>
+      <c r="D7" s="9">
+        <f t="shared" si="0"/>
+        <v>388.09914727809905</v>
+      </c>
+      <c r="E7" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C7/100</f>
         <v>130</v>
       </c>
-      <c r="F7" t="e">
-        <f>(D7*Datos_Usuario!B3)+E7</f>
-        <v>#NUM!</v>
+      <c r="F7" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E7</f>
+        <v>14137.845167846355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f>Bancos!A8</f>
+        <v>Banco Promerica</v>
+      </c>
+      <c r="B8" s="9">
+        <f>-PMT(Bancos!B8/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>360.52144861951484</v>
+      </c>
+      <c r="C8">
+        <f>Datos_Usuario!$B$2*Bancos!D8/100</f>
+        <v>55</v>
+      </c>
+      <c r="D8" s="9">
+        <f t="shared" si="0"/>
+        <v>415.52144861951484</v>
+      </c>
+      <c r="E8" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C8/100</f>
+        <v>150</v>
+      </c>
+      <c r="F8" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E8</f>
+        <v>14157.845167846355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f>Bancos!A9</f>
+        <v>Banco G&amp;T Continental</v>
+      </c>
+      <c r="B9" s="9">
+        <f>-PMT(Bancos!B9/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>364.03714308119442</v>
+      </c>
+      <c r="C9">
+        <f>Datos_Usuario!$B$2*Bancos!D9/100</f>
+        <v>60</v>
+      </c>
+      <c r="D9" s="9">
+        <f t="shared" si="0"/>
+        <v>424.03714308119442</v>
+      </c>
+      <c r="E9" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C9/100</f>
+        <v>180</v>
+      </c>
+      <c r="F9" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E9</f>
+        <v>14187.845167846355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>Bancos!A10</f>
+        <v>Banco Abank</v>
+      </c>
+      <c r="B10" s="9">
+        <f>-PMT(Bancos!B10/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>366.56020023572506</v>
+      </c>
+      <c r="C10">
+        <f>Datos_Usuario!$B$2*Bancos!D10/100</f>
+        <v>60</v>
+      </c>
+      <c r="D10" s="9">
+        <f t="shared" si="0"/>
+        <v>426.56020023572506</v>
+      </c>
+      <c r="E10" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C10/100</f>
+        <v>200</v>
+      </c>
+      <c r="F10" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E10</f>
+        <v>14207.845167846355</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f>Bancos!A11</f>
+        <v>Banco Atlántida SV</v>
+      </c>
+      <c r="B11" s="9">
+        <f>-PMT(Bancos!B11/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>362.52804470908609</v>
+      </c>
+      <c r="C11">
+        <f>Datos_Usuario!$B$2*Bancos!D11/100</f>
+        <v>55</v>
+      </c>
+      <c r="D11" s="9">
+        <f t="shared" si="0"/>
+        <v>417.52804470908609</v>
+      </c>
+      <c r="E11" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C11/100</f>
+        <v>170</v>
+      </c>
+      <c r="F11" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E11</f>
+        <v>14177.845167846355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>Bancos!A12</f>
+        <v>Banco Integral</v>
+      </c>
+      <c r="B12" s="9">
+        <f>-PMT(Bancos!B12/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>374.18836428215747</v>
+      </c>
+      <c r="C12">
+        <f>Datos_Usuario!$B$2*Bancos!D12/100</f>
+        <v>65</v>
+      </c>
+      <c r="D12" s="9">
+        <f t="shared" si="0"/>
+        <v>439.18836428215747</v>
+      </c>
+      <c r="E12" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C12/100</f>
+        <v>250</v>
+      </c>
+      <c r="F12" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E12</f>
+        <v>14257.845167846355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f>Bancos!A13</f>
+        <v>Banco Multivalores</v>
+      </c>
+      <c r="B13" s="9">
+        <f>-PMT(Bancos!B13/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>370.6175645038735</v>
+      </c>
+      <c r="C13">
+        <f>Datos_Usuario!$B$2*Bancos!D13/100</f>
+        <v>60</v>
+      </c>
+      <c r="D13" s="9">
+        <f t="shared" si="0"/>
+        <v>430.6175645038735</v>
+      </c>
+      <c r="E13" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C13/100</f>
+        <v>220</v>
+      </c>
+      <c r="F13" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E13</f>
+        <v>14227.845167846355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f>Bancos!A14</f>
+        <v>Financiera Credicomer</v>
+      </c>
+      <c r="B14" s="9">
+        <f>-PMT(Bancos!B14/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>376.75067336191768</v>
+      </c>
+      <c r="C14">
+        <f>Datos_Usuario!$B$2*Bancos!D14/100</f>
+        <v>70</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" si="0"/>
+        <v>446.75067336191768</v>
+      </c>
+      <c r="E14" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C14/100</f>
+        <v>250</v>
+      </c>
+      <c r="F14" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E14</f>
+        <v>14257.845167846355</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>Bancos!A15</f>
+        <v>Financiera Fiducia</v>
+      </c>
+      <c r="B15" s="9">
+        <f>-PMT(Bancos!B15/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>384.49603279487002</v>
+      </c>
+      <c r="C15">
+        <f>Datos_Usuario!$B$2*Bancos!D15/100</f>
+        <v>75</v>
+      </c>
+      <c r="D15" s="9">
+        <f t="shared" si="0"/>
+        <v>459.49603279487002</v>
+      </c>
+      <c r="E15" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C15/100</f>
+        <v>300</v>
+      </c>
+      <c r="F15" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E15</f>
+        <v>14307.845167846355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f>Bancos!A16</f>
+        <v>FEDECACES</v>
+      </c>
+      <c r="B16" s="9">
+        <f>-PMT(Bancos!B16/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>339.35287330980975</v>
+      </c>
+      <c r="C16">
+        <f>Datos_Usuario!$B$2*Bancos!D16/100</f>
+        <v>30</v>
+      </c>
+      <c r="D16" s="9">
+        <f t="shared" si="0"/>
+        <v>369.35287330980975</v>
+      </c>
+      <c r="E16" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C16/100</f>
+        <v>100</v>
+      </c>
+      <c r="F16" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E16</f>
+        <v>14107.845167846355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f>Bancos!A17</f>
+        <v>CACEP</v>
+      </c>
+      <c r="B17" s="9">
+        <f>-PMT(Bancos!B17/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>345.67467796479883</v>
+      </c>
+      <c r="C17">
+        <f>Datos_Usuario!$B$2*Bancos!D17/100</f>
+        <v>35</v>
+      </c>
+      <c r="D17" s="9">
+        <f t="shared" si="0"/>
+        <v>380.67467796479883</v>
+      </c>
+      <c r="E17" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C17/100</f>
+        <v>120</v>
+      </c>
+      <c r="F17" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E17</f>
+        <v>14127.845167846355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f>Bancos!A18</f>
+        <v>ACODJAR</v>
+      </c>
+      <c r="B18" s="9">
+        <f>-PMT(Bancos!B18/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>347.63349445339361</v>
+      </c>
+      <c r="C18">
+        <f>Datos_Usuario!$B$2*Bancos!D18/100</f>
+        <v>40</v>
+      </c>
+      <c r="D18" s="9">
+        <f t="shared" si="0"/>
+        <v>387.63349445339361</v>
+      </c>
+      <c r="E18" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C18/100</f>
+        <v>100</v>
+      </c>
+      <c r="F18" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E18</f>
+        <v>14107.845167846355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f>Bancos!A19</f>
+        <v>COOPAS</v>
+      </c>
+      <c r="B19" s="9">
+        <f>-PMT(Bancos!B19/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>351.0768276902628</v>
+      </c>
+      <c r="C19">
+        <f>Datos_Usuario!$B$2*Bancos!D19/100</f>
+        <v>45</v>
+      </c>
+      <c r="D19" s="9">
+        <f t="shared" si="0"/>
+        <v>396.0768276902628</v>
+      </c>
+      <c r="E19" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C19/100</f>
+        <v>150</v>
+      </c>
+      <c r="F19" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E19</f>
+        <v>14157.845167846355</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f>Bancos!A20</f>
+        <v>CREDESAN</v>
+      </c>
+      <c r="B20" s="9">
+        <f>-PMT(Bancos!B20/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>353.05323174115546</v>
+      </c>
+      <c r="C20">
+        <f>Datos_Usuario!$B$2*Bancos!D20/100</f>
+        <v>45</v>
+      </c>
+      <c r="D20" s="9">
+        <f t="shared" si="0"/>
+        <v>398.05323174115546</v>
+      </c>
+      <c r="E20" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C20/100</f>
+        <v>150</v>
+      </c>
+      <c r="F20" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E20</f>
+        <v>14157.845167846355</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f>Bancos!A21</f>
+        <v>Caja de Crédito Zacatecoluca</v>
+      </c>
+      <c r="B21" s="9">
+        <f>-PMT(Bancos!B21/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>381.90453178109493</v>
+      </c>
+      <c r="C21">
+        <f>Datos_Usuario!$B$2*Bancos!D21/100</f>
+        <v>70</v>
+      </c>
+      <c r="D21" s="9">
+        <f t="shared" si="0"/>
+        <v>451.90453178109493</v>
+      </c>
+      <c r="E21" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C21/100</f>
+        <v>250</v>
+      </c>
+      <c r="F21" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E21</f>
+        <v>14257.845167846355</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f>Bancos!A22</f>
+        <v>Caja de Crédito San Miguel</v>
+      </c>
+      <c r="B22" s="9">
+        <f>-PMT(Bancos!B22/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>389.70805506767505</v>
+      </c>
+      <c r="C22">
+        <f>Datos_Usuario!$B$2*Bancos!D22/100</f>
+        <v>75</v>
+      </c>
+      <c r="D22" s="9">
+        <f t="shared" si="0"/>
+        <v>464.70805506767505</v>
+      </c>
+      <c r="E22" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C22/100</f>
+        <v>300</v>
+      </c>
+      <c r="F22" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E22</f>
+        <v>14307.845167846355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f>Bancos!A23</f>
+        <v>Caja de Crédito Metapán</v>
+      </c>
+      <c r="B23" s="9">
+        <f>-PMT(Bancos!B23/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>380.87064780414323</v>
+      </c>
+      <c r="C23">
+        <f>Datos_Usuario!$B$2*Bancos!D23/100</f>
+        <v>65</v>
+      </c>
+      <c r="D23" s="9">
+        <f t="shared" si="0"/>
+        <v>445.87064780414323</v>
+      </c>
+      <c r="E23" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C23/100</f>
+        <v>220</v>
+      </c>
+      <c r="F23" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E23</f>
+        <v>14227.845167846355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f>Bancos!A24</f>
+        <v>AMC</v>
+      </c>
+      <c r="B24" s="9">
+        <f>-PMT(Bancos!B24/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>392.32852597798149</v>
+      </c>
+      <c r="C24">
+        <f>Datos_Usuario!$B$2*Bancos!D24/100</f>
+        <v>80</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" si="0"/>
+        <v>472.32852597798149</v>
+      </c>
+      <c r="E24" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C24/100</f>
+        <v>350</v>
+      </c>
+      <c r="F24" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E24</f>
+        <v>14357.845167846355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f>Bancos!A25</f>
+        <v>FUNDAMICRO</v>
+      </c>
+      <c r="B25" s="9">
+        <f>-PMT(Bancos!B25/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
+        <v>405.57444196246786</v>
+      </c>
+      <c r="C25">
+        <f>Datos_Usuario!$B$2*Bancos!D25/100</f>
+        <v>90</v>
+      </c>
+      <c r="D25" s="9">
+        <f t="shared" si="0"/>
+        <v>495.57444196246786</v>
+      </c>
+      <c r="E25" s="9">
+        <f>Datos_Usuario!$B$2*Bancos!C25/100</f>
+        <v>400</v>
+      </c>
+      <c r="F25" s="10">
+        <f>($D$2*Datos_Usuario!$B$3)+E25</f>
+        <v>14407.845167846355</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD63BAB-92C2-443B-BF25-08BC5EFAEC32}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CCA2932-5D16-4340-858D-C9CB9A04474E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,30 +277,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -311,7 +312,28 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -390,54 +412,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -484,6 +458,30 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -498,26 +496,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{080ABFE9-80C2-4A58-8BC4-BBCA16057D04}" name="Tabla1" displayName="Tabla1" ref="A1:D25" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{080ABFE9-80C2-4A58-8BC4-BBCA16057D04}" name="Tabla1" displayName="Tabla1" ref="A1:D25" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:D25" xr:uid="{080ABFE9-80C2-4A58-8BC4-BBCA16057D04}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AA2A3659-7672-4F99-885E-610FAC14686C}" name="Banco" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{C4781AEF-B664-4AF5-895A-39D0F39F0B17}" name="Tasa Anual (%)" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{8E36FA80-3834-4E12-8186-2824F196B054}" name="Comisión Apertura (%)" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{4F8D4ED9-5269-4616-9C6D-A121FCF25265}" name="Seguro Mensual (%)" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{AA2A3659-7672-4F99-885E-610FAC14686C}" name="Banco" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{C4781AEF-B664-4AF5-895A-39D0F39F0B17}" name="Tasa Anual (%)" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{8E36FA80-3834-4E12-8186-2824F196B054}" name="Comisión Apertura (%)" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{4F8D4ED9-5269-4616-9C6D-A121FCF25265}" name="Seguro Mensual (%)" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264891E1-080E-4BAC-9BA3-AA23FF7A4EFB}" name="Tabla3" displayName="Tabla3" ref="A1:G25" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264891E1-080E-4BAC-9BA3-AA23FF7A4EFB}" name="Tabla3" displayName="Tabla3" ref="A1:G25" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:G25" xr:uid="{264891E1-080E-4BAC-9BA3-AA23FF7A4EFB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F5BA89DD-0F6B-44A0-995C-9B338E879CC5}" name="Banco">
       <calculatedColumnFormula>Bancos!A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{86DBCBAC-4201-4193-A97D-A1E2B1CCDF8D}" name="Cuota Base $" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{86DBCBAC-4201-4193-A97D-A1E2B1CCDF8D}" name="Cuota Base $" dataDxfId="3">
       <calculatedColumnFormula>-PMT(Bancos!B2/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{2859AA11-281A-460E-B9E9-B120708B86A6}" name="Seguro Mensual $">
@@ -525,7 +523,7 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{35FF3CC9-8643-471C-8783-0366014B943E}" name="Cuota Total $" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{64796EF2-7559-4746-9DE2-7E951923F98F}" name="Comisión $" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{D6134B07-6059-4D61-B517-A15DC0DE93AB}" name="Costo Total $" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{D6134B07-6059-4D61-B517-A15DC0DE93AB}" name="Costo Total $" dataDxfId="0">
       <calculatedColumnFormula>($D$2*Datos_Usuario!$B$3)+E2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{294D65C5-04E3-49E2-88F6-6F3C4957DEC8}" name="Evaluación"/>
@@ -827,55 +825,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="10">
         <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13">
-        <v>800</v>
+      <c r="B4" s="9">
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="10">
         <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="9">
         <f>B5*B4</f>
-        <v>240</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -908,338 +906,338 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>15.5</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>2</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="4">
         <v>17</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="4">
         <v>1.5</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="4">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>16</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>16.5</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>1.2</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="4">
         <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="3">
         <v>14.5</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="3">
         <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="4">
         <v>12.2</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>1.3</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="4">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>17.8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="3">
         <v>1.5</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="4">
         <v>18.5</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="4">
         <v>1.8</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="4">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>19</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="4">
         <v>18.2</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="4">
         <v>1.7</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="4">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <v>20.5</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>2.5</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>0.65</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="4">
         <v>19.8</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="4">
         <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <v>21</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>2.5</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="4">
         <v>22.5</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="4">
         <v>3</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="4">
         <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>13.5</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="4">
+        <v>14.8</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="C18" s="3">
         <v>1</v>
       </c>
-      <c r="D16" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="8">
-        <v>14.8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="4">
         <v>15.9</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="4">
         <v>1.5</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="4">
         <v>0.45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>16.3</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>1.5</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="3">
         <v>0.45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="4">
         <v>22</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="4">
         <v>2.5</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="4">
         <v>0.7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="3">
         <v>23.5</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>3</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="3">
         <v>0.75</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="4">
         <v>21.8</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="4">
         <v>0.65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>24</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>3.5</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="3">
         <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="4">
         <v>26.5</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="4">
         <v>0.9</v>
       </c>
     </row>
@@ -1287,7 +1285,7 @@
         <f>Bancos!A2</f>
         <v>Banco Agrícola</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="5">
         <f>-PMT(Bancos!B2/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>349.10681021795432</v>
       </c>
@@ -1295,15 +1293,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D2/100</f>
         <v>40</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="5">
         <f t="shared" ref="D2:D25" si="0">B2+C2</f>
         <v>389.10681021795432</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="5">
         <f>Datos_Usuario!B2*Bancos!C2/100</f>
         <v>200</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E2</f>
         <v>14207.845167846355</v>
       </c>
@@ -1313,7 +1311,7 @@
         <f>Bancos!A3</f>
         <v>BAC Credomatic</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="5">
         <f>-PMT(Bancos!B3/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>356.52727526744678</v>
       </c>
@@ -1321,15 +1319,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D3/100</f>
         <v>50</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="5">
         <f t="shared" si="0"/>
         <v>406.52727526744678</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="5">
         <f>Datos_Usuario!B2*Bancos!C3/100</f>
         <v>150</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E3</f>
         <v>14157.845167846355</v>
       </c>
@@ -1339,7 +1337,7 @@
         <f>Bancos!A4</f>
         <v>Banco Cuscatlán</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="5">
         <f>-PMT(Bancos!B4/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>351.57033036350094</v>
       </c>
@@ -1347,15 +1345,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D4/100</f>
         <v>45</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="5">
         <f t="shared" si="0"/>
         <v>396.57033036350094</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="5">
         <f>Datos_Usuario!B2*Bancos!C4/100</f>
         <v>100</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E4</f>
         <v>14107.845167846355</v>
       </c>
@@ -1365,7 +1363,7 @@
         <f>Bancos!A5</f>
         <v>Davivienda</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="5">
         <f>-PMT(Bancos!B5/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>354.04382550022973</v>
       </c>
@@ -1373,15 +1371,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D5/100</f>
         <v>50</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="5">
         <f>B5+C5</f>
         <v>404.04382550022973</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C5/100</f>
         <v>120</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E5</f>
         <v>14127.845167846355</v>
       </c>
@@ -1391,7 +1389,7 @@
         <f>Bancos!A6</f>
         <v>Banco Hipotecario</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="5">
         <f>-PMT(Bancos!B6/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>344.20977442813734</v>
       </c>
@@ -1399,15 +1397,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D6/100</f>
         <v>35</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="5">
         <f>B6+C6</f>
         <v>379.20977442813734</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C6/100</f>
         <v>100</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E6</f>
         <v>14107.845167846355</v>
       </c>
@@ -1417,7 +1415,7 @@
         <f>Bancos!A7</f>
         <v>Banco Azul</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="5">
         <f>-PMT(Bancos!B7/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>333.09914727809905</v>
       </c>
@@ -1425,15 +1423,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D7/100</f>
         <v>55</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>388.09914727809905</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C7/100</f>
         <v>130</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E7</f>
         <v>14137.845167846355</v>
       </c>
@@ -1443,7 +1441,7 @@
         <f>Bancos!A8</f>
         <v>Banco Promerica</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="5">
         <f>-PMT(Bancos!B8/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>360.52144861951484</v>
       </c>
@@ -1451,15 +1449,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D8/100</f>
         <v>55</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>415.52144861951484</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C8/100</f>
         <v>150</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E8</f>
         <v>14157.845167846355</v>
       </c>
@@ -1469,7 +1467,7 @@
         <f>Bancos!A9</f>
         <v>Banco G&amp;T Continental</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="5">
         <f>-PMT(Bancos!B9/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>364.03714308119442</v>
       </c>
@@ -1477,15 +1475,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D9/100</f>
         <v>60</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="5">
         <f t="shared" si="0"/>
         <v>424.03714308119442</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C9/100</f>
         <v>180</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E9</f>
         <v>14187.845167846355</v>
       </c>
@@ -1495,7 +1493,7 @@
         <f>Bancos!A10</f>
         <v>Banco Abank</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="5">
         <f>-PMT(Bancos!B10/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>366.56020023572506</v>
       </c>
@@ -1503,15 +1501,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D10/100</f>
         <v>60</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="5">
         <f t="shared" si="0"/>
         <v>426.56020023572506</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C10/100</f>
         <v>200</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E10</f>
         <v>14207.845167846355</v>
       </c>
@@ -1521,7 +1519,7 @@
         <f>Bancos!A11</f>
         <v>Banco Atlántida SV</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="5">
         <f>-PMT(Bancos!B11/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>362.52804470908609</v>
       </c>
@@ -1529,15 +1527,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D11/100</f>
         <v>55</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="5">
         <f t="shared" si="0"/>
         <v>417.52804470908609</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C11/100</f>
         <v>170</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E11</f>
         <v>14177.845167846355</v>
       </c>
@@ -1547,7 +1545,7 @@
         <f>Bancos!A12</f>
         <v>Banco Integral</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="5">
         <f>-PMT(Bancos!B12/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>374.18836428215747</v>
       </c>
@@ -1555,15 +1553,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D12/100</f>
         <v>65</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="5">
         <f t="shared" si="0"/>
         <v>439.18836428215747</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C12/100</f>
         <v>250</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E12</f>
         <v>14257.845167846355</v>
       </c>
@@ -1573,7 +1571,7 @@
         <f>Bancos!A13</f>
         <v>Banco Multivalores</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="5">
         <f>-PMT(Bancos!B13/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>370.6175645038735</v>
       </c>
@@ -1581,15 +1579,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D13/100</f>
         <v>60</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="5">
         <f t="shared" si="0"/>
         <v>430.6175645038735</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C13/100</f>
         <v>220</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E13</f>
         <v>14227.845167846355</v>
       </c>
@@ -1599,7 +1597,7 @@
         <f>Bancos!A14</f>
         <v>Financiera Credicomer</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="5">
         <f>-PMT(Bancos!B14/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>376.75067336191768</v>
       </c>
@@ -1607,15 +1605,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D14/100</f>
         <v>70</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="5">
         <f t="shared" si="0"/>
         <v>446.75067336191768</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C14/100</f>
         <v>250</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E14</f>
         <v>14257.845167846355</v>
       </c>
@@ -1625,7 +1623,7 @@
         <f>Bancos!A15</f>
         <v>Financiera Fiducia</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="5">
         <f>-PMT(Bancos!B15/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>384.49603279487002</v>
       </c>
@@ -1633,15 +1631,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D15/100</f>
         <v>75</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="5">
         <f t="shared" si="0"/>
         <v>459.49603279487002</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C15/100</f>
         <v>300</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E15</f>
         <v>14307.845167846355</v>
       </c>
@@ -1651,7 +1649,7 @@
         <f>Bancos!A16</f>
         <v>FEDECACES</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="5">
         <f>-PMT(Bancos!B16/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>339.35287330980975</v>
       </c>
@@ -1659,17 +1657,17 @@
         <f>Datos_Usuario!$B$2*Bancos!D16/100</f>
         <v>30</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="5">
         <f t="shared" si="0"/>
         <v>369.35287330980975</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C16/100</f>
-        <v>100</v>
-      </c>
-      <c r="F16" s="10">
+        <v>120</v>
+      </c>
+      <c r="F16" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E16</f>
-        <v>14107.845167846355</v>
+        <v>14127.845167846355</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1677,7 +1675,7 @@
         <f>Bancos!A17</f>
         <v>CACEP</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="5">
         <f>-PMT(Bancos!B17/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>345.67467796479883</v>
       </c>
@@ -1685,15 +1683,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D17/100</f>
         <v>35</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="5">
         <f t="shared" si="0"/>
         <v>380.67467796479883</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C17/100</f>
         <v>120</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E17</f>
         <v>14127.845167846355</v>
       </c>
@@ -1703,7 +1701,7 @@
         <f>Bancos!A18</f>
         <v>ACODJAR</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="5">
         <f>-PMT(Bancos!B18/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>347.63349445339361</v>
       </c>
@@ -1711,15 +1709,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D18/100</f>
         <v>40</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="5">
         <f t="shared" si="0"/>
         <v>387.63349445339361</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C18/100</f>
         <v>100</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E18</f>
         <v>14107.845167846355</v>
       </c>
@@ -1729,7 +1727,7 @@
         <f>Bancos!A19</f>
         <v>COOPAS</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="5">
         <f>-PMT(Bancos!B19/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>351.0768276902628</v>
       </c>
@@ -1737,15 +1735,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D19/100</f>
         <v>45</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="5">
         <f t="shared" si="0"/>
         <v>396.0768276902628</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C19/100</f>
         <v>150</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E19</f>
         <v>14157.845167846355</v>
       </c>
@@ -1755,7 +1753,7 @@
         <f>Bancos!A20</f>
         <v>CREDESAN</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="5">
         <f>-PMT(Bancos!B20/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>353.05323174115546</v>
       </c>
@@ -1763,15 +1761,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D20/100</f>
         <v>45</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="5">
         <f t="shared" si="0"/>
         <v>398.05323174115546</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C20/100</f>
         <v>150</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E20</f>
         <v>14157.845167846355</v>
       </c>
@@ -1781,7 +1779,7 @@
         <f>Bancos!A21</f>
         <v>Caja de Crédito Zacatecoluca</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="5">
         <f>-PMT(Bancos!B21/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>381.90453178109493</v>
       </c>
@@ -1789,15 +1787,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D21/100</f>
         <v>70</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="5">
         <f t="shared" si="0"/>
         <v>451.90453178109493</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C21/100</f>
         <v>250</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E21</f>
         <v>14257.845167846355</v>
       </c>
@@ -1807,7 +1805,7 @@
         <f>Bancos!A22</f>
         <v>Caja de Crédito San Miguel</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="5">
         <f>-PMT(Bancos!B22/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>389.70805506767505</v>
       </c>
@@ -1815,15 +1813,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D22/100</f>
         <v>75</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="5">
         <f t="shared" si="0"/>
         <v>464.70805506767505</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C22/100</f>
         <v>300</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E22</f>
         <v>14307.845167846355</v>
       </c>
@@ -1833,7 +1831,7 @@
         <f>Bancos!A23</f>
         <v>Caja de Crédito Metapán</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="5">
         <f>-PMT(Bancos!B23/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>380.87064780414323</v>
       </c>
@@ -1841,15 +1839,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D23/100</f>
         <v>65</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="5">
         <f t="shared" si="0"/>
         <v>445.87064780414323</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C23/100</f>
         <v>220</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E23</f>
         <v>14227.845167846355</v>
       </c>
@@ -1859,7 +1857,7 @@
         <f>Bancos!A24</f>
         <v>AMC</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="5">
         <f>-PMT(Bancos!B24/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>392.32852597798149</v>
       </c>
@@ -1867,15 +1865,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D24/100</f>
         <v>80</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="5">
         <f t="shared" si="0"/>
         <v>472.32852597798149</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C24/100</f>
         <v>350</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E24</f>
         <v>14357.845167846355</v>
       </c>
@@ -1885,7 +1883,7 @@
         <f>Bancos!A25</f>
         <v>FUNDAMICRO</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="5">
         <f>-PMT(Bancos!B25/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
         <v>405.57444196246786</v>
       </c>
@@ -1893,15 +1891,15 @@
         <f>Datos_Usuario!$B$2*Bancos!D25/100</f>
         <v>90</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="5">
         <f t="shared" si="0"/>
         <v>495.57444196246786</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C25/100</f>
         <v>400</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E25</f>
         <v>14407.845167846355</v>
       </c>

--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CCA2932-5D16-4340-858D-C9CB9A04474E}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5702B7ED-A893-4C4C-846C-7078FC0B856E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Usuario" sheetId="1" r:id="rId1"/>
@@ -1106,7 +1106,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="3">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="C16" s="3">
         <v>1.2</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B16" s="5">
         <f>-PMT(Bancos!B16/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
-        <v>339.35287330980975</v>
+        <v>364.03714308119442</v>
       </c>
       <c r="C16">
         <f>Datos_Usuario!$B$2*Bancos!D16/100</f>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D16" s="5">
         <f t="shared" si="0"/>
-        <v>369.35287330980975</v>
+        <v>394.03714308119442</v>
       </c>
       <c r="E16" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C16/100</f>

--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5702B7ED-A893-4C4C-846C-7078FC0B856E}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C758C09-25F9-4B96-AFBD-095083B720E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -966,10 +966,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D6" s="3">
         <v>0.35</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B6" s="5">
         <f>-PMT(Bancos!B6/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
-        <v>344.20977442813734</v>
+        <v>349.10681021795432</v>
       </c>
       <c r="C6">
         <f>Datos_Usuario!$B$2*Bancos!D6/100</f>
@@ -1399,15 +1399,15 @@
       </c>
       <c r="D6" s="5">
         <f>B6+C6</f>
-        <v>379.20977442813734</v>
+        <v>384.10681021795432</v>
       </c>
       <c r="E6" s="5">
         <f>Datos_Usuario!$B$2*Bancos!C6/100</f>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F6" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E6</f>
-        <v>14107.845167846355</v>
+        <v>14117.845167846355</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">

--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C758C09-25F9-4B96-AFBD-095083B720E2}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B098111-FB76-473E-9CE0-3318A9C7305E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Usuario" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9">
-        <v>460</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
       </c>
       <c r="B6" s="9">
         <f>B5*B4</f>
-        <v>138</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">

--- a/Simulador_Prestamos_Estetico_El_Salvador.xlsx
+++ b/Simulador_Prestamos_Estetico_El_Salvador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millicom-my.sharepoint.com/personal/mjrodriguez_sv_tigo_com/Documents/Escritorio/SIMULADOR PRESTAMOS SV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B098111-FB76-473E-9CE0-3318A9C7305E}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{B3CF3EBC-390B-421A-9E50-A70CC02BC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F50BC61C-501D-41EC-B20E-0CA2149EAB82}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Usuario" sheetId="1" r:id="rId1"/>
@@ -910,7 +910,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B2" s="5">
         <f>-PMT(Bancos!B2/100/12,Datos_Usuario!$B$3,Datos_Usuario!$B$2)</f>
-        <v>349.10681021795432</v>
+        <v>308.77096865371942</v>
       </c>
       <c r="C2">
         <f>Datos_Usuario!$B$2*Bancos!D2/100</f>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D2" s="5">
         <f t="shared" ref="D2:D25" si="0">B2+C2</f>
-        <v>389.10681021795432</v>
+        <v>348.77096865371942</v>
       </c>
       <c r="E2" s="5">
         <f>Datos_Usuario!B2*Bancos!C2/100</f>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F2" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E2</f>
-        <v>14207.845167846355</v>
+        <v>12755.7548715339</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F3" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E3</f>
-        <v>14157.845167846355</v>
+        <v>12705.7548715339</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="F4" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E4</f>
-        <v>14107.845167846355</v>
+        <v>12655.7548715339</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F5" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E5</f>
-        <v>14127.845167846355</v>
+        <v>12675.7548715339</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F6" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E6</f>
-        <v>14117.845167846355</v>
+        <v>12665.7548715339</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="F7" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E7</f>
-        <v>14137.845167846355</v>
+        <v>12685.7548715339</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F8" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E8</f>
-        <v>14157.845167846355</v>
+        <v>12705.7548715339</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F9" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E9</f>
-        <v>14187.845167846355</v>
+        <v>12735.7548715339</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="F10" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E10</f>
-        <v>14207.845167846355</v>
+        <v>12755.7548715339</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E11</f>
-        <v>14177.845167846355</v>
+        <v>12725.7548715339</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F12" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E12</f>
-        <v>14257.845167846355</v>
+        <v>12805.7548715339</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F13" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E13</f>
-        <v>14227.845167846355</v>
+        <v>12775.7548715339</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F14" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E14</f>
-        <v>14257.845167846355</v>
+        <v>12805.7548715339</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F15" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E15</f>
-        <v>14307.845167846355</v>
+        <v>12855.7548715339</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F16" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E16</f>
-        <v>14127.845167846355</v>
+        <v>12675.7548715339</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F17" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E17</f>
-        <v>14127.845167846355</v>
+        <v>12675.7548715339</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F18" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E18</f>
-        <v>14107.845167846355</v>
+        <v>12655.7548715339</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="F19" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E19</f>
-        <v>14157.845167846355</v>
+        <v>12705.7548715339</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F20" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E20</f>
-        <v>14157.845167846355</v>
+        <v>12705.7548715339</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F21" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E21</f>
-        <v>14257.845167846355</v>
+        <v>12805.7548715339</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F22" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E22</f>
-        <v>14307.845167846355</v>
+        <v>12855.7548715339</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F23" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E23</f>
-        <v>14227.845167846355</v>
+        <v>12775.7548715339</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F24" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E24</f>
-        <v>14357.845167846355</v>
+        <v>12905.7548715339</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F25" s="6">
         <f>($D$2*Datos_Usuario!$B$3)+E25</f>
-        <v>14407.845167846355</v>
+        <v>12955.7548715339</v>
       </c>
     </row>
   </sheetData>
